--- a/ConvertData/EXCEL_Bolts/TableBoltsSP43.xlsx
+++ b/ConvertData/EXCEL_Bolts/TableBoltsSP43.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Disk\YandexDisk\Programmings\ForWorking\ConvertData\ConvertData\EXCEL_Bolts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F020763-ABC6-4705-B594-FAF54D09921F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8507A921-61C7-4B65-8EF2-EF3569CB35E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,27 +25,40 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="5">
   <si>
-    <t>Ab</t>
+    <t>GOST_bolts</t>
   </si>
   <si>
-    <t>Abn</t>
+    <t>СП 43.13330</t>
   </si>
   <si>
-    <t>d</t>
+    <t>d_SP43</t>
+  </si>
+  <si>
+    <t>Ab_SP43</t>
+  </si>
+  <si>
+    <t>Abn_SP43</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFA31515"/>
+      <name val="Cascadia Mono"/>
+      <family val="3"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="2">
@@ -68,8 +81,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -408,186 +424,238 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+    <row r="1" spans="1:4" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
       <c r="C1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
         <v>16</v>
       </c>
-      <c r="B2">
+      <c r="C2">
         <v>2.0099999999999998</v>
       </c>
-      <c r="C2">
+      <c r="D2">
         <v>1.57</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3">
         <v>18</v>
       </c>
-      <c r="B3">
+      <c r="C3">
         <v>2.54</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>1.92</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4">
         <v>20</v>
-      </c>
-      <c r="B4">
-        <v>2.4900000000000002</v>
       </c>
       <c r="C4">
         <v>2.4900000000000002</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5">
+      <c r="D4">
+        <v>2.4900000000000002</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5">
         <v>24</v>
-      </c>
-      <c r="B5">
-        <v>3.59</v>
       </c>
       <c r="C5">
         <v>3.59</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6">
+      <c r="D5">
+        <v>3.59</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6">
         <v>27</v>
-      </c>
-      <c r="B6">
-        <v>4.67</v>
       </c>
       <c r="C6">
         <v>4.67</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7">
+      <c r="D6">
+        <v>4.67</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7">
         <v>30</v>
-      </c>
-      <c r="B7">
-        <v>5.6</v>
       </c>
       <c r="C7">
         <v>5.6</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8">
+      <c r="D7">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8">
         <v>36</v>
-      </c>
-      <c r="B8">
-        <v>8.1999999999999993</v>
       </c>
       <c r="C8">
         <v>8.1999999999999993</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9">
+      <c r="D8">
+        <v>8.1999999999999993</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9">
         <v>42</v>
-      </c>
-      <c r="B9">
-        <v>11.3</v>
       </c>
       <c r="C9">
         <v>11.3</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10">
+      <c r="D9">
+        <v>11.3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10">
         <v>48</v>
-      </c>
-      <c r="B10">
-        <v>14.8</v>
       </c>
       <c r="C10">
         <v>14.8</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A11">
+      <c r="D10">
+        <v>14.8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11">
         <v>56</v>
-      </c>
-      <c r="B11">
-        <v>20.5</v>
       </c>
       <c r="C11">
         <v>20.5</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12">
+      <c r="D11">
+        <v>20.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>1</v>
+      </c>
+      <c r="B12">
         <v>64</v>
-      </c>
-      <c r="B12">
-        <v>26.9</v>
       </c>
       <c r="C12">
         <v>26.9</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A13">
+      <c r="D12">
+        <v>26.9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>1</v>
+      </c>
+      <c r="B13">
         <v>72</v>
-      </c>
-      <c r="B13">
-        <v>34.700000000000003</v>
       </c>
       <c r="C13">
         <v>34.700000000000003</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A14">
+      <c r="D13">
+        <v>34.700000000000003</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>1</v>
+      </c>
+      <c r="B14">
         <v>80</v>
-      </c>
-      <c r="B14">
-        <v>43.5</v>
       </c>
       <c r="C14">
         <v>43.5</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A15">
+      <c r="D14">
+        <v>43.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>1</v>
+      </c>
+      <c r="B15">
         <v>90</v>
-      </c>
-      <c r="B15">
-        <v>56</v>
       </c>
       <c r="C15">
         <v>56</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A16">
+      <c r="D15">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>1</v>
+      </c>
+      <c r="B16">
         <v>100</v>
-      </c>
-      <c r="B16">
-        <v>70.2</v>
       </c>
       <c r="C16">
         <v>70.2</v>
       </c>
+      <c r="D16">
+        <v>70.2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/ConvertData/EXCEL_Bolts/TableBoltsSP43.xlsx
+++ b/ConvertData/EXCEL_Bolts/TableBoltsSP43.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Disk\YandexDisk\Programmings\ForWorking\ConvertData\ConvertData\EXCEL_Bolts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8507A921-61C7-4B65-8EF2-EF3569CB35E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F020763-ABC6-4705-B594-FAF54D09921F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,40 +25,27 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
-    <t>GOST_bolts</t>
+    <t>Ab</t>
   </si>
   <si>
-    <t>СП 43.13330</t>
+    <t>Abn</t>
   </si>
   <si>
-    <t>d_SP43</t>
-  </si>
-  <si>
-    <t>Ab_SP43</t>
-  </si>
-  <si>
-    <t>Abn_SP43</t>
+    <t>d</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FFA31515"/>
-      <name val="Cascadia Mono"/>
-      <family val="3"/>
-      <charset val="204"/>
     </font>
   </fonts>
   <fills count="2">
@@ -81,11 +68,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -424,238 +408,186 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>2</v>
-      </c>
       <c r="C1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
         <v>1</v>
       </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>16</v>
+      </c>
       <c r="B2">
-        <v>16</v>
+        <v>2.0099999999999998</v>
       </c>
       <c r="C2">
-        <v>2.0099999999999998</v>
-      </c>
-      <c r="D2">
         <v>1.57</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>1</v>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>18</v>
       </c>
       <c r="B3">
-        <v>18</v>
+        <v>2.54</v>
       </c>
       <c r="C3">
-        <v>2.54</v>
-      </c>
-      <c r="D3">
         <v>1.92</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>1</v>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>20</v>
       </c>
       <c r="B4">
-        <v>20</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="C4">
         <v>2.4900000000000002</v>
       </c>
-      <c r="D4">
-        <v>2.4900000000000002</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>1</v>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>24</v>
       </c>
       <c r="B5">
-        <v>24</v>
+        <v>3.59</v>
       </c>
       <c r="C5">
         <v>3.59</v>
       </c>
-      <c r="D5">
-        <v>3.59</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>1</v>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>27</v>
       </c>
       <c r="B6">
-        <v>27</v>
+        <v>4.67</v>
       </c>
       <c r="C6">
         <v>4.67</v>
       </c>
-      <c r="D6">
-        <v>4.67</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>1</v>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>30</v>
       </c>
       <c r="B7">
-        <v>30</v>
+        <v>5.6</v>
       </c>
       <c r="C7">
         <v>5.6</v>
       </c>
-      <c r="D7">
-        <v>5.6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>1</v>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>36</v>
       </c>
       <c r="B8">
-        <v>36</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="C8">
         <v>8.1999999999999993</v>
       </c>
-      <c r="D8">
-        <v>8.1999999999999993</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>1</v>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>42</v>
       </c>
       <c r="B9">
-        <v>42</v>
+        <v>11.3</v>
       </c>
       <c r="C9">
         <v>11.3</v>
       </c>
-      <c r="D9">
-        <v>11.3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>1</v>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>48</v>
       </c>
       <c r="B10">
-        <v>48</v>
+        <v>14.8</v>
       </c>
       <c r="C10">
         <v>14.8</v>
       </c>
-      <c r="D10">
-        <v>14.8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>1</v>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>56</v>
       </c>
       <c r="B11">
-        <v>56</v>
+        <v>20.5</v>
       </c>
       <c r="C11">
         <v>20.5</v>
       </c>
-      <c r="D11">
-        <v>20.5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>1</v>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>64</v>
       </c>
       <c r="B12">
-        <v>64</v>
+        <v>26.9</v>
       </c>
       <c r="C12">
         <v>26.9</v>
       </c>
-      <c r="D12">
-        <v>26.9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>1</v>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>72</v>
       </c>
       <c r="B13">
-        <v>72</v>
+        <v>34.700000000000003</v>
       </c>
       <c r="C13">
         <v>34.700000000000003</v>
       </c>
-      <c r="D13">
-        <v>34.700000000000003</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>1</v>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>80</v>
       </c>
       <c r="B14">
-        <v>80</v>
+        <v>43.5</v>
       </c>
       <c r="C14">
         <v>43.5</v>
       </c>
-      <c r="D14">
-        <v>43.5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>1</v>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>90</v>
       </c>
       <c r="B15">
-        <v>90</v>
+        <v>56</v>
       </c>
       <c r="C15">
         <v>56</v>
       </c>
-      <c r="D15">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>1</v>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>100</v>
       </c>
       <c r="B16">
-        <v>100</v>
+        <v>70.2</v>
       </c>
       <c r="C16">
         <v>70.2</v>
       </c>
-      <c r="D16">
-        <v>70.2</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>